--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486741_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486741_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8036</v>
+        <v>6.5552</v>
       </c>
       <c r="E2" t="n">
         <v>5.4113</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3923</v>
+        <v>1.1439</v>
       </c>
       <c r="G2" t="n">
         <v>3.1344</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2484</v>
+        <v>0.0001</v>
       </c>
       <c r="T2" t="n">
         <v>-0.1383</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3866</v>
+        <v>0.1383</v>
       </c>
       <c r="V2" t="n">
         <v>2.4554</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. MURRAY</t>
+          <t>G. ZALAZAR RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8394</v>
+        <v>1.5787</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9401</v>
+        <v>4.5179</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1008</v>
+        <v>-2.9392</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1672</v>
+        <v>-1.0492</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7866</v>
+        <v>-1.1103</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6194</v>
+        <v>0.0611</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5897</v>
+        <v>1.7938</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2016</v>
+        <v>-0.0059</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3881</v>
+        <v>1.7996</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.4225</v>
+        <v>-2.8429</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4149</v>
+        <v>-1.1044</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0075</v>
+        <v>-1.7385</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.7377</v>
+        <v>1.3515</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1239</v>
+        <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2248</v>
+        <v>-1.1791</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7993</v>
+        <v>-0.9589</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4256</v>
+        <v>-0.2201</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1851</v>
+        <v>2.4554</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4128</v>
+        <v>3.6831</v>
       </c>
       <c r="X3" t="n">
         <v>-1.2277</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. ZALAZAR RODRIGUEZ</t>
+          <t>C. MURRAY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5664</v>
+        <v>0.4078</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2076</v>
+        <v>1.9059</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6412</v>
+        <v>-1.4981</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.0492</v>
+        <v>1.1672</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1103</v>
+        <v>1.7866</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0611</v>
+        <v>-0.6194</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7938</v>
+        <v>3.5897</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0059</v>
+        <v>2.2016</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7996</v>
+        <v>1.3881</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8429</v>
+        <v>-2.4225</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1044</v>
+        <v>-0.4149</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7385</v>
+        <v>-2.0075</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3515</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3515</v>
+        <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1913</v>
+        <v>-0.2067</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2692</v>
+        <v>-0.235</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0282</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4554</v>
+        <v>1.1851</v>
       </c>
       <c r="W4" t="n">
-        <v>3.6831</v>
+        <v>2.4128</v>
       </c>
       <c r="X4" t="n">
         <v>-1.2277</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4361</v>
+        <v>-0.3368</v>
       </c>
       <c r="E5" t="n">
         <v>0.9397</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3758</v>
+        <v>-1.2765</v>
       </c>
       <c r="G5" t="n">
         <v>1.3457</v>
@@ -844,13 +844,13 @@
         <v>0.1931</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0095</v>
+        <v>-0.9102</v>
       </c>
       <c r="T5" t="n">
         <v>-0.6622</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3474</v>
+        <v>-0.248</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.061</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7981</v>
+        <v>1.2118</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8591</v>
+        <v>-1.7597</v>
       </c>
       <c r="G6" t="n">
         <v>1.2313</v>
@@ -922,13 +922,13 @@
         <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0646</v>
+        <v>-0.5516</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7174</v>
+        <v>-0.3037</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3472</v>
+        <v>-0.2479</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2277</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7507</v>
+        <v>-1.4568</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1295</v>
+        <v>0.0261</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8802</v>
+        <v>-1.4829</v>
       </c>
       <c r="G7" t="n">
         <v>0.1323</v>
@@ -1000,13 +1000,13 @@
         <v>1.5446</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9489</v>
+        <v>-0.655</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2486</v>
+        <v>-0.352</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7003</v>
+        <v>-0.303</v>
       </c>
       <c r="V7" t="n">
         <v>-1.5133</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9402</v>
+        <v>-1.5306</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6829</v>
+        <v>-1.3726</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2573</v>
+        <v>-0.1579</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6282</v>
@@ -1078,13 +1078,13 @@
         <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.513</v>
+        <v>-0.1034</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4415</v>
+        <v>-0.1312</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0716</v>
+        <v>0.0278</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5712</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.319</v>
+        <v>-4.9673</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8091</v>
+        <v>-2.7056</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.51</v>
+        <v>-2.2617</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8515</v>
@@ -1156,13 +1156,13 @@
         <v>0.7723</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1586</v>
+        <v>-0.8068</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7725</v>
+        <v>-0.6691</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.386</v>
+        <v>-0.1377</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1851</v>
@@ -1189,22 +1189,22 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2975999999999992</v>
+        <v>-0.297699999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>9.9343</v>
+        <v>9.9345</v>
       </c>
       <c r="F10" t="n">
         <v>-10.2321</v>
       </c>
       <c r="G10" t="n">
-        <v>3.481999999999999</v>
+        <v>3.482</v>
       </c>
       <c r="H10" t="n">
-        <v>6.895499999999998</v>
+        <v>6.8955</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.413599999999999</v>
+        <v>-3.4136</v>
       </c>
       <c r="J10" t="n">
         <v>14.9052</v>
@@ -1225,7 +1225,7 @@
         <v>-9.3483</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9654999999999999</v>
+        <v>-0.9654999999999997</v>
       </c>
       <c r="Q10" t="n">
         <v>-11.5848</v>
@@ -1240,7 +1240,7 @@
         <v>-3.4504</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9625000000000001</v>
+        <v>-0.9623999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>1.5986</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.194</v>
+        <v>5.9553</v>
       </c>
       <c r="E11" t="n">
-        <v>5.3155</v>
+        <v>5.7291</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1215</v>
+        <v>0.2262</v>
       </c>
       <c r="G11" t="n">
         <v>5.6244</v>
@@ -1312,13 +1312,13 @@
         <v>1.7377</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0443</v>
+        <v>0.7171</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4142</v>
+        <v>-0.0005</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3699</v>
+        <v>0.7175</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.1071</v>
+        <v>2.9552</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0463</v>
+        <v>2.7703</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0608</v>
+        <v>0.1849</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2309</v>
@@ -1390,13 +1390,13 @@
         <v>1.7377</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.662</v>
+        <v>0.1861</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0209</v>
+        <v>-0.297</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3589</v>
+        <v>0.4831</v>
       </c>
       <c r="V12" t="n">
         <v>2.4554</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1122</v>
+        <v>1.2116</v>
       </c>
       <c r="E13" t="n">
         <v>1.0669</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0453</v>
+        <v>0.1446</v>
       </c>
       <c r="G13" t="n">
         <v>1.4873</v>
@@ -1468,13 +1468,13 @@
         <v>0.3862</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7613</v>
+        <v>-0.6619</v>
       </c>
       <c r="T13" t="n">
         <v>-0.2759</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4854</v>
+        <v>-0.386</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>M. THIAW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.154</v>
+        <v>-0.4755</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5727</v>
+        <v>1.8564</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.7267</v>
+        <v>-2.3319</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.9273</v>
+        <v>-0.2021</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6418</v>
+        <v>-0.028</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.2855</v>
+        <v>-0.1741</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.03</v>
+        <v>1.1574</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1862</v>
+        <v>1.076</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.2162</v>
+        <v>0.0814</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8973</v>
+        <v>-1.3594</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.828</v>
+        <v>-1.1039</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0693</v>
+        <v>-0.2555</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7377</v>
+        <v>0.3862</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7377</v>
+        <v>0.5792</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7499</v>
+        <v>0.8964</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6339</v>
+        <v>0.6065</v>
       </c>
       <c r="U14" t="n">
-        <v>0.116</v>
+        <v>0.2898</v>
       </c>
       <c r="V14" t="n">
+        <v>-1.5559</v>
+      </c>
+      <c r="W14" t="n">
         <v>0.2856</v>
       </c>
-      <c r="W14" t="n">
-        <v>3.9687</v>
-      </c>
       <c r="X14" t="n">
-        <v>-3.6831</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. THIAW</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2356</v>
+        <v>-0.6008</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2701</v>
+        <v>2.9521</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5057</v>
+        <v>-3.5529</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2021</v>
+        <v>-2.9273</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.028</v>
+        <v>-0.6418</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1741</v>
+        <v>-2.2855</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1574</v>
+        <v>-1.03</v>
       </c>
       <c r="K15" t="n">
-        <v>1.076</v>
+        <v>0.1862</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0814</v>
+        <v>-1.2162</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3594</v>
+        <v>-1.8973</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1039</v>
+        <v>-0.828</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2555</v>
+        <v>-1.0693</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3862</v>
+        <v>1.7377</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5792</v>
+        <v>1.7377</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1362</v>
+        <v>0.3032</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0202</v>
+        <v>0.0134</v>
       </c>
       <c r="U15" t="n">
-        <v>0.116</v>
+        <v>0.2898</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.5559</v>
+        <v>0.2856</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2856</v>
+        <v>3.9687</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8415</v>
+        <v>-3.6831</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. DAMIAN</t>
+          <t>I. KANE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9082</v>
+        <v>-1.0399</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2228</v>
+        <v>1.6701</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3146</v>
+        <v>-2.71</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6188</v>
+        <v>-0.0574</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4952</v>
+        <v>-0.0619</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1236</v>
+        <v>0.0045</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2309</v>
+        <v>1.971</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0229</v>
+        <v>0.6282</v>
       </c>
       <c r="L16" t="n">
-        <v>0.208</v>
+        <v>1.3428</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8497</v>
+        <v>-2.0285</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5181</v>
+        <v>-0.6901</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3316</v>
+        <v>-1.3384</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.8962</v>
+        <v>0.7723</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.02</v>
+        <v>-0.1931</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1239</v>
+        <v>0.9654</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9776</v>
+        <v>0.3724</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7095</v>
+        <v>0.2204</v>
       </c>
       <c r="U16" t="n">
-        <v>2.2682</v>
+        <v>0.152</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3709</v>
+        <v>-2.1271</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8568</v>
+        <v>-0.3282</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2277</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. KANE</t>
+          <t>K. RYTZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9654</v>
+        <v>-2.069</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6701</v>
+        <v>-0.5999</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.6355</v>
+        <v>-1.4692</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0574</v>
+        <v>-0.9861</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0619</v>
+        <v>-0.1655</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0045</v>
+        <v>-0.8206</v>
       </c>
       <c r="J17" t="n">
-        <v>1.971</v>
+        <v>-0.6481</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6282</v>
+        <v>0.0414</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3428</v>
+        <v>-0.6895</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0285</v>
+        <v>-0.3381</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6901</v>
+        <v>-0.2069</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3384</v>
+        <v>-0.1311</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7723</v>
+        <v>0.1931</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4469</v>
+        <v>-0.0483</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2204</v>
+        <v>0.0482</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2265</v>
+        <v>-0.0965</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.1271</v>
+        <v>-1.2277</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7989</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. RYTZ</t>
+          <t>L. BUENO CASTILLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1973</v>
+        <v>-2.7533</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7033</v>
+        <v>-2.9561</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.494</v>
+        <v>0.2029</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9861</v>
+        <v>-3.5711</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1655</v>
+        <v>-4.2064</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8206</v>
+        <v>0.6353</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6481</v>
+        <v>-1.2596</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0414</v>
+        <v>-2.6884</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6895</v>
+        <v>1.4288</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3381</v>
+        <v>-2.3115</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2069</v>
+        <v>-1.5179</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1311</v>
+        <v>-0.7935</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1931</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1931</v>
+        <v>2.1239</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1765</v>
+        <v>0.6481</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0552</v>
+        <v>-0.028</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1213</v>
+        <v>0.6761</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2277</v>
+        <v>0.9421</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. BUENO CASTILLO</t>
+          <t>D. DAMIAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6551</v>
+        <v>-2.886</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.7835</v>
+        <v>-2.257</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1284</v>
+        <v>-0.629</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.5711</v>
+        <v>-1.6188</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.2064</v>
+        <v>-0.4952</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6353</v>
+        <v>-1.1236</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2596</v>
+        <v>1.2309</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.6884</v>
+        <v>1.0229</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4288</v>
+        <v>0.208</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3115</v>
+        <v>-2.8497</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5179</v>
+        <v>-1.5181</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7935</v>
+        <v>-1.3316</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7723</v>
+        <v>-2.8962</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.8962</v>
+        <v>-5.02</v>
       </c>
       <c r="R19" t="n">
         <v>2.1239</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2538</v>
+        <v>1.9998</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8554</v>
+        <v>0.6752</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6016</v>
+        <v>1.3245</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9421</v>
+        <v>-0.3709</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2277</v>
+        <v>0.8568</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="20">
@@ -1969,22 +1969,22 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2976999999999999</v>
+        <v>0.297600000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>10.232</v>
+        <v>10.2319</v>
       </c>
       <c r="F20" t="n">
-        <v>-9.934300000000002</v>
+        <v>-9.9344</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.482</v>
+        <v>-3.482000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-6.895700000000001</v>
+        <v>-6.8957</v>
       </c>
       <c r="I20" t="n">
-        <v>3.413599999999999</v>
+        <v>3.4136</v>
       </c>
       <c r="J20" t="n">
         <v>11.4229</v>
@@ -2005,7 +2005,7 @@
         <v>-5.9346</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9654</v>
+        <v>0.9653999999999998</v>
       </c>
       <c r="Q20" t="n">
         <v>-10.6194</v>
@@ -2014,19 +2014,19 @@
         <v>11.5848</v>
       </c>
       <c r="S20" t="n">
-        <v>4.4127</v>
+        <v>4.4129</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9624000000000005</v>
+        <v>0.9623000000000002</v>
       </c>
       <c r="U20" t="n">
-        <v>3.4504</v>
+        <v>3.4503</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5985</v>
       </c>
       <c r="W20" t="n">
-        <v>8.466000000000001</v>
+        <v>8.465999999999999</v>
       </c>
       <c r="X20" t="n">
         <v>-10.0645</v>
